--- a/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>41500</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>36520.516756917001</v>
+        <v>35358.098881814622</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>13479.483243082999</v>
+        <v>14641.901118185378</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1967,87 +1967,93 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="19"/>
-      <c r="B39" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A39" s="19">
+        <v>46201</v>
+      </c>
+      <c r="B39" s="24">
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="C39" s="20"/>
-      <c r="D39" s="21" t="str">
+      <c r="D39" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E39" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E39" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F39" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G39" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H39" s="21" t="str">
+        <v>113.73153394300861</v>
+      </c>
+      <c r="F39" s="21">
+        <f t="shared" si="5"/>
+        <v>386.26846605699137</v>
+      </c>
+      <c r="G39" s="21">
+        <f t="shared" si="4"/>
+        <v>36134.248290860007</v>
+      </c>
+      <c r="H39" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>13865.751709139993</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A40" s="2">
+        <v>46201</v>
+      </c>
+      <c r="B40" s="23">
+        <f t="shared" si="3"/>
+        <v>39</v>
       </c>
       <c r="C40" s="3"/>
-      <c r="D40" s="4" t="str">
+      <c r="D40" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E40" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E40" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F40" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G40" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H40" s="4" t="str">
+        <v>112.52862365970452</v>
+      </c>
+      <c r="F40" s="4">
+        <f t="shared" si="5"/>
+        <v>387.47137634029548</v>
+      </c>
+      <c r="G40" s="4">
+        <f t="shared" si="4"/>
+        <v>35746.776914519709</v>
+      </c>
+      <c r="H40" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>14253.223085480291</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="19"/>
-      <c r="B41" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A41" s="19">
+        <v>46203</v>
+      </c>
+      <c r="B41" s="24">
+        <f t="shared" si="3"/>
+        <v>40</v>
       </c>
       <c r="C41" s="20"/>
-      <c r="D41" s="21" t="str">
+      <c r="D41" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E41" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E41" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F41" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G41" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H41" s="21" t="str">
+        <v>111.32196729491351</v>
+      </c>
+      <c r="F41" s="21">
+        <f t="shared" si="5"/>
+        <v>388.67803270508648</v>
+      </c>
+      <c r="G41" s="21">
+        <f t="shared" si="4"/>
+        <v>35358.098881814622</v>
+      </c>
+      <c r="H41" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>14641.901118185378</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>40000</v>
+        <v>39500</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>35358.098881814622</v>
+        <v>34968.21043499728</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>14641.901118185378</v>
+        <v>15031.78956500272</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -2057,31 +2057,33 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A42" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B42" s="23">
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="4" t="str">
+      <c r="D42" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E42" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E42" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F42" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G42" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H42" s="4" t="str">
+        <v>110.11155318265624</v>
+      </c>
+      <c r="F42" s="4">
+        <f t="shared" si="5"/>
+        <v>389.88844681734378</v>
+      </c>
+      <c r="G42" s="4">
+        <f t="shared" si="4"/>
+        <v>34968.21043499728</v>
+      </c>
+      <c r="H42" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>15031.78956500272</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>39500</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>34968.21043499728</v>
+        <v>34184.787209487964</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>15031.78956500272</v>
+        <v>15815.212790512036</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -2087,59 +2087,63 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="19"/>
-      <c r="B43" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A43" s="19">
+        <v>46213</v>
+      </c>
+      <c r="B43" s="24">
+        <f t="shared" si="3"/>
+        <v>42</v>
       </c>
       <c r="C43" s="20"/>
-      <c r="D43" s="21" t="str">
+      <c r="D43" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E43" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E43" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F43" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G43" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H43" s="21" t="str">
+        <v>108.89736962062339</v>
+      </c>
+      <c r="F43" s="21">
+        <f t="shared" si="5"/>
+        <v>391.10263037937659</v>
+      </c>
+      <c r="G43" s="21">
+        <f t="shared" si="4"/>
+        <v>34577.107804617903</v>
+      </c>
+      <c r="H43" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>15422.892195382097</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A44" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B44" s="23">
+        <f t="shared" si="3"/>
+        <v>43</v>
       </c>
       <c r="C44" s="3"/>
-      <c r="D44" s="4" t="str">
+      <c r="D44" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E44" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E44" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F44" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G44" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H44" s="4" t="str">
+        <v>107.67940487006254</v>
+      </c>
+      <c r="F44" s="4">
+        <f t="shared" si="5"/>
+        <v>392.32059512993749</v>
+      </c>
+      <c r="G44" s="4">
+        <f t="shared" si="4"/>
+        <v>34184.787209487964</v>
+      </c>
+      <c r="H44" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>15815.212790512036</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>38500</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>34184.787209487964</v>
+        <v>33000.479646859734</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>15815.212790512036</v>
+        <v>16999.520353140266</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -2147,87 +2147,93 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="19"/>
-      <c r="B45" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A45" s="19">
+        <v>46217</v>
+      </c>
+      <c r="B45" s="24">
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
       <c r="C45" s="20"/>
-      <c r="D45" s="21" t="str">
+      <c r="D45" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E45" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E45" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F45" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G45" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H45" s="21" t="str">
+        <v>106.45764715566462</v>
+      </c>
+      <c r="F45" s="21">
+        <f t="shared" si="5"/>
+        <v>393.54235284433537</v>
+      </c>
+      <c r="G45" s="21">
+        <f t="shared" si="4"/>
+        <v>33791.244856643629</v>
+      </c>
+      <c r="H45" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>16208.755143356371</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="2"/>
-      <c r="B46" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A46" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B46" s="23">
+        <f t="shared" si="3"/>
+        <v>45</v>
       </c>
       <c r="C46" s="3"/>
-      <c r="D46" s="4" t="str">
+      <c r="D46" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E46" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E46" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F46" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G46" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H46" s="4" t="str">
+        <v>105.23208466545013</v>
+      </c>
+      <c r="F46" s="4">
+        <f t="shared" si="5"/>
+        <v>394.76791533454985</v>
+      </c>
+      <c r="G46" s="4">
+        <f t="shared" si="4"/>
+        <v>33396.476941309076</v>
+      </c>
+      <c r="H46" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>16603.523058690924</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="19"/>
-      <c r="B47" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A47" s="19">
+        <v>46224</v>
+      </c>
+      <c r="B47" s="24">
+        <f t="shared" si="3"/>
+        <v>46</v>
       </c>
       <c r="C47" s="20"/>
-      <c r="D47" s="21" t="str">
+      <c r="D47" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E47" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E47" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F47" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G47" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H47" s="21" t="str">
+        <v>104.00270555065492</v>
+      </c>
+      <c r="F47" s="21">
+        <f t="shared" si="5"/>
+        <v>395.99729444934508</v>
+      </c>
+      <c r="G47" s="21">
+        <f t="shared" si="4"/>
+        <v>33000.479646859734</v>
+      </c>
+      <c r="H47" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>16999.520353140266</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>37000</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>33000.479646859734</v>
+        <v>31001.918071958298</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>16999.520353140266</v>
+        <v>18998.081928041702</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -2237,143 +2237,153 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="2"/>
-      <c r="B48" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A48" s="2">
+        <v>46231</v>
+      </c>
+      <c r="B48" s="23">
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="C48" s="3"/>
-      <c r="D48" s="4" t="str">
+      <c r="D48" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E48" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E48" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F48" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G48" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H48" s="4" t="str">
+        <v>102.76949792561564</v>
+      </c>
+      <c r="F48" s="4">
+        <f t="shared" si="5"/>
+        <v>397.23050207438439</v>
+      </c>
+      <c r="G48" s="4">
+        <f t="shared" si="4"/>
+        <v>32603.24914478535</v>
+      </c>
+      <c r="H48" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>17396.75085521465</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="19"/>
-      <c r="B49" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A49" s="19">
+        <v>46239</v>
+      </c>
+      <c r="B49" s="24">
+        <f t="shared" si="3"/>
+        <v>48</v>
       </c>
       <c r="C49" s="20"/>
-      <c r="D49" s="21" t="str">
+      <c r="D49" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E49" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E49" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F49" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G49" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H49" s="21" t="str">
+        <v>101.53244986765478</v>
+      </c>
+      <c r="F49" s="21">
+        <f t="shared" si="5"/>
+        <v>398.4675501323452</v>
+      </c>
+      <c r="G49" s="21">
+        <f t="shared" si="4"/>
+        <v>32204.781594653006</v>
+      </c>
+      <c r="H49" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>17795.218405346994</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="2"/>
-      <c r="B50" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A50" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B50" s="23">
+        <f t="shared" si="3"/>
+        <v>49</v>
       </c>
       <c r="C50" s="3"/>
-      <c r="D50" s="4" t="str">
+      <c r="D50" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E50" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E50" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F50" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G50" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H50" s="4" t="str">
+        <v>100.29154941696548</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" si="5"/>
+        <v>399.70845058303451</v>
+      </c>
+      <c r="G50" s="4">
+        <f t="shared" si="4"/>
+        <v>31805.073144069971</v>
+      </c>
+      <c r="H50" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>18194.926855930029</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="19"/>
-      <c r="B51" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A51" s="19">
+        <v>46239</v>
+      </c>
+      <c r="B51" s="24">
+        <f t="shared" si="3"/>
+        <v>50</v>
       </c>
       <c r="C51" s="20"/>
-      <c r="D51" s="21" t="str">
+      <c r="D51" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E51" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E51" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F51" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G51" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H51" s="21" t="str">
+        <v>99.046784576495867</v>
+      </c>
+      <c r="F51" s="21">
+        <f t="shared" si="5"/>
+        <v>400.95321542350416</v>
+      </c>
+      <c r="G51" s="21">
+        <f t="shared" si="4"/>
+        <v>31404.119928646465</v>
+      </c>
+      <c r="H51" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>18595.880071353535</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="2"/>
-      <c r="B52" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A52" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B52" s="23">
+        <f t="shared" si="3"/>
+        <v>51</v>
       </c>
       <c r="C52" s="3"/>
-      <c r="D52" s="4" t="str">
+      <c r="D52" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E52" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E52" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F52" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G52" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H52" s="4" t="str">
+        <v>97.79814331183303</v>
+      </c>
+      <c r="F52" s="4">
+        <f t="shared" si="5"/>
+        <v>402.20185668816697</v>
+      </c>
+      <c r="G52" s="4">
+        <f t="shared" si="4"/>
+        <v>31001.918071958298</v>
+      </c>
+      <c r="H52" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>18998.081928041702</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>34500</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>31001.918071958298</v>
+        <v>29380.546280768685</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>18998.081928041702</v>
+        <v>20619.453719231315</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -2387,115 +2387,123 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="19"/>
-      <c r="B53" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A53" s="19">
+        <v>46242</v>
+      </c>
+      <c r="B53" s="24">
+        <f t="shared" si="3"/>
+        <v>52</v>
       </c>
       <c r="C53" s="20"/>
-      <c r="D53" s="21" t="str">
+      <c r="D53" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E53" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E53" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F53" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G53" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H53" s="21" t="str">
+        <v>96.545613551086774</v>
+      </c>
+      <c r="F53" s="21">
+        <f t="shared" si="5"/>
+        <v>403.45438644891323</v>
+      </c>
+      <c r="G53" s="21">
+        <f t="shared" si="4"/>
+        <v>30598.463685509385</v>
+      </c>
+      <c r="H53" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>19401.536314490615</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="2"/>
-      <c r="B54" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A54" s="2">
+        <v>46243</v>
+      </c>
+      <c r="B54" s="23">
+        <f t="shared" si="3"/>
+        <v>53</v>
       </c>
       <c r="C54" s="3"/>
-      <c r="D54" s="4" t="str">
+      <c r="D54" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E54" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E54" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F54" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G54" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H54" s="4" t="str">
+        <v>95.289183184772753</v>
+      </c>
+      <c r="F54" s="4">
+        <f t="shared" si="5"/>
+        <v>404.71081681522725</v>
+      </c>
+      <c r="G54" s="4">
+        <f t="shared" si="4"/>
+        <v>30193.752868694159</v>
+      </c>
+      <c r="H54" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>19806.247131305841</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="19"/>
-      <c r="B55" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A55" s="19">
+        <v>46244</v>
+      </c>
+      <c r="B55" s="24">
+        <f t="shared" si="3"/>
+        <v>54</v>
       </c>
       <c r="C55" s="20"/>
-      <c r="D55" s="21" t="str">
+      <c r="D55" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E55" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E55" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F55" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G55" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H55" s="21" t="str">
+        <v>94.028840065695562</v>
+      </c>
+      <c r="F55" s="21">
+        <f t="shared" si="5"/>
+        <v>405.97115993430441</v>
+      </c>
+      <c r="G55" s="21">
+        <f t="shared" si="4"/>
+        <v>29787.781708759856</v>
+      </c>
+      <c r="H55" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>20212.218291240144</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="2"/>
-      <c r="B56" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A56" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B56" s="23">
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="C56" s="3"/>
-      <c r="D56" s="4" t="str">
+      <c r="D56" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E56" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E56" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F56" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G56" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H56" s="4" t="str">
+        <v>92.76457200883118</v>
+      </c>
+      <c r="F56" s="4">
+        <f t="shared" si="5"/>
+        <v>407.23542799116882</v>
+      </c>
+      <c r="G56" s="4">
+        <f t="shared" si="4"/>
+        <v>29380.546280768685</v>
+      </c>
+      <c r="H56" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>20619.453719231315</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>32500</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>29380.546280768685</v>
+        <v>26910.362742211062</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>20619.453719231315</v>
+        <v>23089.637257788938</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -2507,171 +2507,183 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="19"/>
-      <c r="B57" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A57" s="19">
+        <v>46256</v>
+      </c>
+      <c r="B57" s="24">
+        <f t="shared" si="3"/>
+        <v>56</v>
       </c>
       <c r="C57" s="20"/>
-      <c r="D57" s="21" t="str">
+      <c r="D57" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E57" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E57" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F57" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G57" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H57" s="21" t="str">
+        <v>91.496366791209184</v>
+      </c>
+      <c r="F57" s="21">
+        <f t="shared" si="5"/>
+        <v>408.5036332087908</v>
+      </c>
+      <c r="G57" s="21">
+        <f t="shared" si="4"/>
+        <v>28972.042647559894</v>
+      </c>
+      <c r="H57" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>21027.957352440106</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="2"/>
-      <c r="B58" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A58" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B58" s="23">
+        <f t="shared" si="3"/>
+        <v>57</v>
       </c>
       <c r="C58" s="3"/>
-      <c r="D58" s="4" t="str">
+      <c r="D58" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E58" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E58" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F58" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G58" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H58" s="4" t="str">
+        <v>90.22421215179466</v>
+      </c>
+      <c r="F58" s="4">
+        <f t="shared" si="5"/>
+        <v>409.77578784820537</v>
+      </c>
+      <c r="G58" s="4">
+        <f t="shared" si="4"/>
+        <v>28562.26685971169</v>
+      </c>
+      <c r="H58" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>21437.73314028831</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="19"/>
-      <c r="B59" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A59" s="19">
+        <v>46259</v>
+      </c>
+      <c r="B59" s="24">
+        <f t="shared" si="3"/>
+        <v>58</v>
       </c>
       <c r="C59" s="20"/>
-      <c r="D59" s="21" t="str">
+      <c r="D59" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E59" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E59" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F59" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G59" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H59" s="21" t="str">
+        <v>88.948095791369553</v>
+      </c>
+      <c r="F59" s="21">
+        <f t="shared" si="5"/>
+        <v>411.05190420863045</v>
+      </c>
+      <c r="G59" s="21">
+        <f t="shared" si="4"/>
+        <v>28151.214955503059</v>
+      </c>
+      <c r="H59" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>21848.785044496941</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="2"/>
-      <c r="B60" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A60" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B60" s="23">
+        <f t="shared" si="3"/>
+        <v>59</v>
       </c>
       <c r="C60" s="3"/>
-      <c r="D60" s="4" t="str">
+      <c r="D60" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E60" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E60" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F60" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G60" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H60" s="4" t="str">
+        <v>87.668005372413802</v>
+      </c>
+      <c r="F60" s="4">
+        <f t="shared" si="5"/>
+        <v>412.3319946275862</v>
+      </c>
+      <c r="G60" s="4">
+        <f t="shared" si="4"/>
+        <v>27738.882960875471</v>
+      </c>
+      <c r="H60" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>22261.117039124529</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="19"/>
-      <c r="B61" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A61" s="19">
+        <v>46271</v>
+      </c>
+      <c r="B61" s="24">
+        <f t="shared" si="3"/>
+        <v>60</v>
       </c>
       <c r="C61" s="20"/>
-      <c r="D61" s="21" t="str">
+      <c r="D61" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E61" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E61" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F61" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G61" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H61" s="21" t="str">
+        <v>86.383928518986096</v>
+      </c>
+      <c r="F61" s="21">
+        <f t="shared" si="5"/>
+        <v>413.61607148101393</v>
+      </c>
+      <c r="G61" s="21">
+        <f t="shared" si="4"/>
+        <v>27325.266889394457</v>
+      </c>
+      <c r="H61" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>22674.733110605543</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="2"/>
-      <c r="B62" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A62" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B62" s="23">
+        <f t="shared" si="3"/>
+        <v>61</v>
       </c>
       <c r="C62" s="3"/>
-      <c r="D62" s="4" t="str">
+      <c r="D62" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E62" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E62" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F62" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G62" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H62" s="4" t="str">
+        <v>85.095852816604165</v>
+      </c>
+      <c r="F62" s="4">
+        <f t="shared" si="5"/>
+        <v>414.90414718339582</v>
+      </c>
+      <c r="G62" s="4">
+        <f t="shared" si="4"/>
+        <v>26910.362742211062</v>
+      </c>
+      <c r="H62" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>23089.637257788938</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
